--- a/SQExcel.Portal/src/content/docs/ja/docs/images/small-scale/B社販売管理システム_共通コードとサービスマスター.xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/small-scale/B社販売管理システム_共通コードとサービスマスター.xlsx
@@ -136,7 +136,7 @@
     <x:t>処理結果</x:t>
   </x:si>
   <x:si>
-    <x:t>[INSERT] データ取り込み成功 処理件数：30件</x:t>
+    <x:t>[INSERT] データ取り込み成功 処理件数：22件</x:t>
   </x:si>
   <x:si>
     <x:t>項目名</x:t>
@@ -1303,6 +1303,9 @@
     <x:t>サービスマスター（広告種別・料金定義）</x:t>
   </x:si>
   <x:si>
+    <x:t>[INSERT] データ取り込み成功 処理件数：30件</x:t>
+  </x:si>
+  <x:si>
     <x:t>service_id</x:t>
   </x:si>
   <x:si>
@@ -3361,7 +3364,10 @@
     <x:phoneticPr fontId="0"/>
   </x:si>
   <x:si>
-    <x:t>[INSERT] データ取り込み成功 処理件数：22件</x:t>
+    <x:t>DB種類</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PostgreSQL</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3458,7 +3464,7 @@
       <x:diagonal/>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="0" hidden="0"/>
@@ -3532,8 +3538,14 @@
     <x:xf numFmtId="2" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="0" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="176" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="51">
+  <x:cellXfs count="53">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <x:alignment vertical="top"/>
@@ -3717,6 +3729,14 @@
     <x:xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="0" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -4063,8 +4083,8 @@
     <x:col min="2" max="2" width="24.726562" style="2" customWidth="1"/>
     <x:col min="3" max="3" width="14.90625" style="2" customWidth="1"/>
     <x:col min="4" max="4" width="33.542969" style="2" customWidth="1"/>
-    <x:col min="5" max="5" width="50.726562" style="2" customWidth="1"/>
-    <x:col min="6" max="6" width="22.726562" style="3" customWidth="1"/>
+    <x:col min="5" max="5" width="18.710625" style="2" customWidth="1"/>
+    <x:col min="6" max="6" width="24.710625" style="3" customWidth="1"/>
     <x:col min="7" max="7" width="30.726562" style="2" customWidth="1"/>
     <x:col min="8" max="8" width="22.726562" style="3" customWidth="1"/>
     <x:col min="9" max="9" width="30.726562" style="2" customWidth="1"/>
@@ -4086,8 +4106,12 @@
       <x:c r="D1" s="32" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E1" s="9"/>
-      <x:c r="F1" s="8"/>
+      <x:c r="E1" s="33" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="F1" s="51" t="s">
+        <x:v>198</x:v>
+      </x:c>
       <x:c r="G1" s="9"/>
       <x:c r="H1" s="8"/>
       <x:c r="I1" s="9"/>
@@ -4097,7 +4121,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B2" s="29" t="s">
-        <x:v>196</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C2" s="9"/>
       <x:c r="D2" s="9"/>
@@ -4878,8 +4902,9 @@
     <x:col min="2" max="2" width="24.726562" style="2" customWidth="1"/>
     <x:col min="3" max="3" width="36.726562" style="2" customWidth="1"/>
     <x:col min="4" max="4" width="14" style="2" customWidth="1"/>
-    <x:col min="5" max="5" width="20.816406" style="2" customWidth="1"/>
-    <x:col min="6" max="7" width="14.726562" style="1" customWidth="1"/>
+    <x:col min="5" max="5" width="18.710625" style="2" customWidth="1"/>
+    <x:col min="6" max="6" width="24.710625" style="1" customWidth="1"/>
+    <x:col min="7" max="7" width="14.726562" style="1" customWidth="1"/>
     <x:col min="8" max="8" width="14.089844" style="1" customWidth="1"/>
     <x:col min="9" max="9" width="19.179688" style="24" customWidth="1"/>
     <x:col min="10" max="10" width="28.726562" style="24" customWidth="1"/>
@@ -4907,7 +4932,12 @@
       <x:c r="D1" s="32" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="E1" s="9"/>
+      <x:c r="E1" s="33" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="F1" s="52" t="s">
+        <x:v>198</x:v>
+      </x:c>
       <x:c r="I1" s="25"/>
       <x:c r="J1" s="25"/>
       <x:c r="K1" s="9"/>
@@ -4921,7 +4951,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B2" s="29" t="s">
-        <x:v>5</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C2" s="9"/>
       <x:c r="D2" s="9"/>
@@ -4939,16 +4969,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="35" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C3" s="36" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D3" s="36" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="E3" s="36" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="F3" s="46" t="s">
         <x:v>52</x:v>
@@ -4957,16 +4987,16 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="H3" s="46" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="I3" s="47" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="J3" s="47" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="K3" s="36" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="L3" s="46" t="s">
         <x:v>66</x:v>
@@ -4995,37 +5025,37 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="35" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C4" s="36" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D4" s="36" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E4" s="36" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="F4" s="40" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="G4" s="40" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H4" s="40" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I4" s="48" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="J4" s="48" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="K4" s="36" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="L4" s="40" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="M4" s="39" t="s">
         <x:v>22</x:v>
@@ -5047,37 +5077,37 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B5" s="35" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C5" s="36" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="D5" s="36" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E5" s="36" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="F5" s="46" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G5" s="46" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="H5" s="46" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="I5" s="47" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="J5" s="47" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="K5" s="36" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="L5" s="46" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="I5" s="47" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="J5" s="47" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="K5" s="36" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="L5" s="46" t="s">
-        <x:v>127</x:v>
       </x:c>
       <x:c r="M5" s="37" t="s">
         <x:v>30</x:v>
@@ -5196,16 +5226,16 @@
     </x:row>
     <x:row r="8" spans="1:18" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B8" s="2" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D8" s="2" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E8" s="2" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="F8" s="1">
         <x:v>1</x:v>
@@ -5220,16 +5250,16 @@
         <x:v>35000</x:v>
       </x:c>
       <x:c r="K8" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L8" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N8" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P8" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q8" s="30" t="s">
         <x:v>44</x:v>
@@ -5240,16 +5270,16 @@
     </x:row>
     <x:row r="9" spans="1:18" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B9" s="2" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D9" s="2" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E9" s="2" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F9" s="1">
         <x:v>1</x:v>
@@ -5264,16 +5294,16 @@
         <x:v>42500</x:v>
       </x:c>
       <x:c r="K9" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L9" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N9" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P9" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q9" s="30" t="s">
         <x:v>44</x:v>
@@ -5284,16 +5314,16 @@
     </x:row>
     <x:row r="10" spans="1:18" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B10" s="2" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D10" s="2" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E10" s="2" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>1</x:v>
@@ -5308,16 +5338,16 @@
         <x:v>50000</x:v>
       </x:c>
       <x:c r="K10" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L10" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N10" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P10" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q10" s="30" t="s">
         <x:v>44</x:v>
@@ -5328,16 +5358,16 @@
     </x:row>
     <x:row r="11" spans="1:18" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B11" s="2" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D11" s="2" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E11" s="2" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="F11" s="1">
         <x:v>1</x:v>
@@ -5352,16 +5382,16 @@
         <x:v>25000</x:v>
       </x:c>
       <x:c r="K11" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L11" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N11" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P11" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q11" s="30" t="s">
         <x:v>44</x:v>
@@ -5372,16 +5402,16 @@
     </x:row>
     <x:row r="12" spans="1:18" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B12" s="2" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C12" s="2" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D12" s="2" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E12" s="2" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F12" s="1">
         <x:v>1</x:v>
@@ -5396,16 +5426,16 @@
         <x:v>32000</x:v>
       </x:c>
       <x:c r="K12" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L12" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N12" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P12" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q12" s="30" t="s">
         <x:v>44</x:v>
@@ -5416,16 +5446,16 @@
     </x:row>
     <x:row r="13" spans="1:18" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B13" s="2" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E13" s="2" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F13" s="1">
         <x:v>1</x:v>
@@ -5440,16 +5470,16 @@
         <x:v>40000</x:v>
       </x:c>
       <x:c r="K13" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L13" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N13" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P13" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q13" s="30" t="s">
         <x:v>44</x:v>
@@ -5460,10 +5490,10 @@
     </x:row>
     <x:row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <x:c r="B14" s="2" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C14" s="2" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D14" s="2" t="s">
         <x:v>45</x:v>
@@ -5481,16 +5511,16 @@
         <x:v>35000</x:v>
       </x:c>
       <x:c r="K14" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L14" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N14" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P14" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q14" s="30" t="s">
         <x:v>44</x:v>
@@ -5501,10 +5531,10 @@
     </x:row>
     <x:row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <x:c r="B15" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C15" s="2" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="D15" s="2" t="s">
         <x:v>45</x:v>
@@ -5522,16 +5552,16 @@
         <x:v>42500</x:v>
       </x:c>
       <x:c r="K15" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L15" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N15" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P15" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q15" s="30" t="s">
         <x:v>44</x:v>
@@ -5542,10 +5572,10 @@
     </x:row>
     <x:row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <x:c r="B16" s="2" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C16" s="2" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D16" s="2" t="s">
         <x:v>45</x:v>
@@ -5563,16 +5593,16 @@
         <x:v>50000</x:v>
       </x:c>
       <x:c r="K16" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L16" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N16" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P16" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q16" s="30" t="s">
         <x:v>44</x:v>
@@ -5583,10 +5613,10 @@
     </x:row>
     <x:row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <x:c r="B17" s="2" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C17" s="2" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D17" s="2" t="s">
         <x:v>45</x:v>
@@ -5604,16 +5634,16 @@
         <x:v>30000</x:v>
       </x:c>
       <x:c r="K17" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L17" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N17" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P17" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q17" s="30" t="s">
         <x:v>44</x:v>
@@ -5624,10 +5654,10 @@
     </x:row>
     <x:row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <x:c r="B18" s="2" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C18" s="2" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="D18" s="2" t="s">
         <x:v>45</x:v>
@@ -5645,16 +5675,16 @@
         <x:v>40000</x:v>
       </x:c>
       <x:c r="K18" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L18" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N18" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P18" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q18" s="30" t="s">
         <x:v>44</x:v>
@@ -5665,10 +5695,10 @@
     </x:row>
     <x:row r="19" spans="1:18" x14ac:dyDescent="0.35">
       <x:c r="B19" s="2" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C19" s="2" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D19" s="2" t="s">
         <x:v>45</x:v>
@@ -5686,16 +5716,16 @@
         <x:v>50000</x:v>
       </x:c>
       <x:c r="K19" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L19" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N19" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P19" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q19" s="30" t="s">
         <x:v>44</x:v>
@@ -5706,10 +5736,10 @@
     </x:row>
     <x:row r="20" spans="1:18" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B20" s="2" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C20" s="2" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D20" s="2" t="s">
         <x:v>36</x:v>
@@ -5727,16 +5757,16 @@
         <x:v>15000</x:v>
       </x:c>
       <x:c r="K20" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L20" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N20" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P20" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q20" s="30" t="s">
         <x:v>44</x:v>
@@ -5747,10 +5777,10 @@
     </x:row>
     <x:row r="21" spans="1:18" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B21" s="2" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C21" s="2" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="D21" s="2" t="s">
         <x:v>36</x:v>
@@ -5768,16 +5798,16 @@
         <x:v>20000</x:v>
       </x:c>
       <x:c r="K21" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L21" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N21" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P21" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q21" s="30" t="s">
         <x:v>44</x:v>
@@ -5788,10 +5818,10 @@
     </x:row>
     <x:row r="22" spans="1:18" ht="18.5" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B22" s="2" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C22" s="2" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="D22" s="2" t="s">
         <x:v>36</x:v>
@@ -5809,16 +5839,16 @@
         <x:v>25000</x:v>
       </x:c>
       <x:c r="K22" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L22" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N22" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P22" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q22" s="30" t="s">
         <x:v>44</x:v>
@@ -5829,10 +5859,10 @@
     </x:row>
     <x:row r="23" spans="1:18" ht="37" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B23" s="2" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C23" s="2" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="D23" s="2" t="s">
         <x:v>36</x:v>
@@ -5850,16 +5880,16 @@
         <x:v>20000</x:v>
       </x:c>
       <x:c r="K23" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L23" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N23" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P23" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q23" s="30" t="s">
         <x:v>44</x:v>
@@ -5870,10 +5900,10 @@
     </x:row>
     <x:row r="24" spans="1:18" ht="37" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B24" s="2" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C24" s="2" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="D24" s="2" t="s">
         <x:v>36</x:v>
@@ -5891,16 +5921,16 @@
         <x:v>30000</x:v>
       </x:c>
       <x:c r="K24" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L24" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N24" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P24" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q24" s="30" t="s">
         <x:v>44</x:v>
@@ -5911,10 +5941,10 @@
     </x:row>
     <x:row r="25" spans="1:18" ht="37" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B25" s="2" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C25" s="2" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="D25" s="2" t="s">
         <x:v>36</x:v>
@@ -5932,16 +5962,16 @@
         <x:v>40000</x:v>
       </x:c>
       <x:c r="K25" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L25" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N25" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P25" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q25" s="30" t="s">
         <x:v>44</x:v>
@@ -5952,10 +5982,10 @@
     </x:row>
     <x:row r="26" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B26" s="2" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C26" s="2" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D26" s="2" t="s">
         <x:v>36</x:v>
@@ -5973,16 +6003,16 @@
         <x:v>10000</x:v>
       </x:c>
       <x:c r="K26" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L26" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N26" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P26" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q26" s="30" t="s">
         <x:v>44</x:v>
@@ -5993,10 +6023,10 @@
     </x:row>
     <x:row r="27" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B27" s="2" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C27" s="2" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="D27" s="2" t="s">
         <x:v>36</x:v>
@@ -6014,16 +6044,16 @@
         <x:v>15000</x:v>
       </x:c>
       <x:c r="K27" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L27" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N27" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P27" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q27" s="30" t="s">
         <x:v>44</x:v>
@@ -6034,10 +6064,10 @@
     </x:row>
     <x:row r="28" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B28" s="2" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C28" s="2" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="D28" s="2" t="s">
         <x:v>36</x:v>
@@ -6055,16 +6085,16 @@
         <x:v>20000</x:v>
       </x:c>
       <x:c r="K28" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L28" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N28" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P28" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q28" s="30" t="s">
         <x:v>44</x:v>
@@ -6075,10 +6105,10 @@
     </x:row>
     <x:row r="29" spans="1:18" ht="37" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B29" s="2" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C29" s="2" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D29" s="2" t="s">
         <x:v>36</x:v>
@@ -6096,16 +6126,16 @@
         <x:v>15000</x:v>
       </x:c>
       <x:c r="K29" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L29" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N29" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P29" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q29" s="30" t="s">
         <x:v>44</x:v>
@@ -6116,10 +6146,10 @@
     </x:row>
     <x:row r="30" spans="1:18" ht="37" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B30" s="2" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C30" s="2" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D30" s="2" t="s">
         <x:v>36</x:v>
@@ -6137,16 +6167,16 @@
         <x:v>25000</x:v>
       </x:c>
       <x:c r="K30" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L30" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N30" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P30" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q30" s="30" t="s">
         <x:v>44</x:v>
@@ -6157,10 +6187,10 @@
     </x:row>
     <x:row r="31" spans="1:18" ht="37" customHeight="1" x14ac:dyDescent="0.35">
       <x:c r="B31" s="2" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C31" s="2" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="D31" s="2" t="s">
         <x:v>36</x:v>
@@ -6178,16 +6208,16 @@
         <x:v>35000</x:v>
       </x:c>
       <x:c r="K31" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L31" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N31" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P31" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q31" s="30" t="s">
         <x:v>44</x:v>
@@ -6198,10 +6228,10 @@
     </x:row>
     <x:row r="32" spans="1:18" x14ac:dyDescent="0.35">
       <x:c r="B32" s="2" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C32" s="2" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="D32" s="2" t="s">
         <x:v>50</x:v>
@@ -6222,16 +6252,16 @@
         <x:v>40000</x:v>
       </x:c>
       <x:c r="K32" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L32" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N32" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P32" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q32" s="30" t="s">
         <x:v>44</x:v>
@@ -6242,10 +6272,10 @@
     </x:row>
     <x:row r="33" spans="1:18" x14ac:dyDescent="0.35">
       <x:c r="B33" s="2" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C33" s="2" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="D33" s="2" t="s">
         <x:v>50</x:v>
@@ -6266,16 +6296,16 @@
         <x:v>50000</x:v>
       </x:c>
       <x:c r="K33" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L33" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N33" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P33" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q33" s="30" t="s">
         <x:v>44</x:v>
@@ -6286,10 +6316,10 @@
     </x:row>
     <x:row r="34" spans="1:18" x14ac:dyDescent="0.35">
       <x:c r="B34" s="2" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C34" s="2" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="D34" s="2" t="s">
         <x:v>50</x:v>
@@ -6310,16 +6340,16 @@
         <x:v>60000</x:v>
       </x:c>
       <x:c r="K34" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L34" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N34" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P34" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q34" s="30" t="s">
         <x:v>44</x:v>
@@ -6330,10 +6360,10 @@
     </x:row>
     <x:row r="35" spans="1:18" x14ac:dyDescent="0.35">
       <x:c r="B35" s="2" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C35" s="2" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D35" s="2" t="s">
         <x:v>50</x:v>
@@ -6354,16 +6384,16 @@
         <x:v>25000</x:v>
       </x:c>
       <x:c r="K35" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L35" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N35" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P35" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q35" s="30" t="s">
         <x:v>44</x:v>
@@ -6374,10 +6404,10 @@
     </x:row>
     <x:row r="36" spans="1:18" x14ac:dyDescent="0.35">
       <x:c r="B36" s="2" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C36" s="2" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="D36" s="2" t="s">
         <x:v>50</x:v>
@@ -6398,16 +6428,16 @@
         <x:v>35000</x:v>
       </x:c>
       <x:c r="K36" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L36" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N36" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P36" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q36" s="30" t="s">
         <x:v>44</x:v>
@@ -6418,10 +6448,10 @@
     </x:row>
     <x:row r="37" spans="1:18" x14ac:dyDescent="0.35">
       <x:c r="B37" s="2" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C37" s="2" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="D37" s="2" t="s">
         <x:v>50</x:v>
@@ -6442,16 +6472,16 @@
         <x:v>45000</x:v>
       </x:c>
       <x:c r="K37" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L37" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N37" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="P37" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Q37" s="30" t="s">
         <x:v>44</x:v>
